--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -736,6 +736,31 @@
         <v>1165</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1019</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -761,6 +761,31 @@
         <v>1019</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -786,6 +786,31 @@
         <v>998</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>949</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -811,6 +811,31 @@
         <v>949</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>965</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -836,6 +836,31 @@
         <v>965</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -861,6 +861,31 @@
         <v>840</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>777</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -886,6 +886,31 @@
         <v>777</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>979</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -911,6 +911,31 @@
         <v>979</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>943</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -936,6 +936,31 @@
         <v>943</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>890</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
